--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_UDO.xlsx
@@ -635,13 +635,13 @@
         <v>81.8</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -654,13 +654,13 @@
         <v>110.8</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="4">
@@ -673,13 +673,13 @@
         <v>100.5</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.9</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="5">
@@ -692,13 +692,13 @@
         <v>10.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +711,13 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -733,10 +733,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -749,13 +749,13 @@
         <v>0.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -768,13 +768,13 @@
         <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -809,7 +809,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
+          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Foul profile sits near league average; physicality is part of the game, but not their defining trait.</t>
+          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_UDO.xlsx
@@ -422,23 +422,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UDO_J._ARAMBURU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -484,11 +855,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,32 +917,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>M. Morgan</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
@@ -632,16 +1037,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1056,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>110.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1075,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100.5</v>
+        <v>104.3</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1094,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.3</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1113,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="7">
@@ -733,10 +1138,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -752,10 +1157,10 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -765,16 +1170,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="10">
@@ -790,10 +1195,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +1214,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>-0</v>
@@ -865,7 +1270,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Above-average assist profile; expect cleaner passing sequences and more extra-pass possessions.</t>
+          <t>Below-average assist profile; more possessions end through direct creation than collective flow.</t>
         </is>
       </c>
     </row>
@@ -889,7 +1294,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
+          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
         </is>
       </c>
     </row>
@@ -901,7 +1306,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Above-average foul volume; contact pressure and discipline both matter in this matchup.</t>
+          <t>Lower foul volume than league average; this is not a team that wants constant contact chaos.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -956,6 +1361,30 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Know the first reference: M. Morgan is a primary scorer, and the plan should start with taking away his comfort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Closeout discipline matters: G. Powell, M. Morgan are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -970,7 +1399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -992,48 +1421,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from M. Morgan and J. Turner; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are M. Morgan and J. Turner; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+          <t>Priority closeouts start with G. Powell, M. Morgan, and P. Nixon; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially P. Nixon, M. Morgan, and C. Rodger; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from M. Morgan and P. Nixon; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially M. Morgan, P. Nixon, and G. Powell; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Do not lose G. Powell and M. Morgan in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1513,270 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>UDO_M._MORGAN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UDO_J._ARAMBURU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>inside scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1173,37 +1885,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1219,41 +1931,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1265,41 +1977,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UDO_D._ARAUJO</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D. Araujo</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1316,36 +2028,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1357,110 +2069,140 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>26</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.4%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>36.6%</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>20</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>28.2%</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>14.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1478,23 +2220,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -1514,15 +2256,15 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1530,26 +2272,18 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>UDO_P._NIXON</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>P. Nixon</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1558,42 +2292,34 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>UDO_M._MORGAN</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>M. Morgan</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -1602,42 +2328,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>UDO_C._RODGER</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>C. Rodger</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -1646,23 +2364,23 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
     </row>
@@ -1674,12 +2392,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1694,19 +2412,283 @@
         </is>
       </c>
       <c r="K14" t="n">
+        <v>13</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>46.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UDO_P._NIXON</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UDO_G._POWELL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UDO_C._RODGER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UDO_J._TURNER</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>6</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>60.0%</t>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UDO_S._VICTO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UDO_J._ARAMBURU</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>41.7%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_UDO.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,41 +515,41 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -567,21 +567,21 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -619,36 +619,36 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -671,31 +671,31 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -723,21 +723,21 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -775,39 +775,143 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UDO_S._VICTO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UDO_T._DIAS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -824,24 +928,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>J. Aramburu | M. Morgan</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +1022,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -944,7 +1106,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
     </row>
@@ -961,7 +1123,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
     </row>
@@ -978,7 +1140,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -1037,16 +1199,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.5</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="3">
@@ -1056,16 +1218,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94.59999999999999</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>-11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -1075,16 +1237,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104.3</v>
+        <v>100.3</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="5">
@@ -1094,16 +1256,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="6">
@@ -1113,16 +1275,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.5</v>
+        <v>18.3</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -1138,7 +1300,7 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1157,10 +1319,10 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1332,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
@@ -1179,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="10">
@@ -1195,10 +1357,10 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1270,7 +1432,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Below-average assist profile; more possessions end through direct creation than collective flow.</t>
+          <t>Ball movement is close to league average; they can share it but are not purely pass-first.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1456,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1534,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Know the first reference: M. Morgan is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Know the first reference: P. Nixon is a primary scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1546,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Closeout discipline matters: G. Powell, M. Morgan are the first perimeter names you cannot lose in help situations.</t>
+          <t>Closeout discipline matters: G. Powell, J. Turner are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1438,7 +1600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with G. Powell, M. Morgan, and P. Nixon; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with G. Powell, J. Turner, and M. Morgan; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Paint Non-RA; protect that area early in possessions.</t>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
         </is>
       </c>
     </row>
@@ -1474,19 +1636,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially M. Morgan, P. Nixon, and G. Powell; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially G. Powell, M. Morgan, and P. Nixon; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+          <t>Recognize the main duo/trio combinations: J. Aramburu | M. Morgan.</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1660,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Do not lose G. Powell and M. Morgan in help-and-recover situations.</t>
+          <t>Offensive rebounding is around league average; box-outs matter but this is not their main edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Do not lose G. Powell and J. Turner in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1697,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1580,17 +1754,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.3</v>
+        <v>26.6</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1600,7 +1774,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>primary handler</t>
         </is>
       </c>
     </row>
@@ -1616,17 +1790,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>24.7</v>
       </c>
       <c r="D3" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1652,27 +1826,27 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="D4" t="n">
-        <v>14.5</v>
+        <v>16.3</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>primary scorer</t>
         </is>
       </c>
     </row>
@@ -1688,17 +1862,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1724,10 +1898,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1735,12 +1909,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>inside scorer</t>
+          <t>paint finisher</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1930,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1776,7 +1950,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1899,23 +2073,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1936,36 +2110,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -1982,36 +2156,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -2023,34 +2197,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UDO_M._MORGAN</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M. Morgan</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
         <v>0.9</v>
@@ -2074,36 +2248,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -2120,32 +2294,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2166,36 +2340,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -2207,38 +2381,48 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>45</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>48.9%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>31.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UDO_D._ARAUJO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D. Araujo</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2260,19 +2444,19 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -2292,23 +2476,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
     </row>
@@ -2328,23 +2512,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>25.6%</t>
         </is>
       </c>
     </row>
@@ -2364,42 +2548,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.3%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>UDO_M._MORGAN</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>M. Morgan</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2408,23 +2584,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2612,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UDO_P._NIXON</t>
+          <t>UDO_G._POWELL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>P. Nixon</t>
+          <t>G. Powell</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2452,23 +2628,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2656,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UDO_G._POWELL</t>
+          <t>UDO_M._MORGAN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>G. Powell</t>
+          <t>M. Morgan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2500,19 +2676,19 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -2524,12 +2700,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UDO_C._RODGER</t>
+          <t>UDO_P._NIXON</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C. Rodger</t>
+          <t>P. Nixon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2540,23 +2716,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2744,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UDO_J._TURNER</t>
+          <t>UDO_C._RODGER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>J. Turner</t>
+          <t>C. Rodger</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2584,23 +2760,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2788,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UDO_S._VICTO</t>
+          <t>UDO_J._ARAMBURU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S. Victo</t>
+          <t>J. Aramburu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2628,23 +2804,23 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2832,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UDO_J._ARAMBURU</t>
+          <t>UDO_J._TURNER</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>J. Aramburu</t>
+          <t>J. Turner</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2672,23 +2848,67 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>26.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UDO_S._VICTO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>35.3%</t>
         </is>
       </c>
     </row>
